--- a/REIT_Pairs_Analytics_2026-08-23.xlsx
+++ b/REIT_Pairs_Analytics_2026-08-23.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
-    <t xml:space="preserve">Report Created: August 23, 2026 08:30 AM   |   Last Data Point in Analysis: August 21, 2026</t>
+    <t xml:space="preserve">Report Created: August 23, 2026 09:28 AM   |   Last Data Point in Analysis: August 21, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Recommendation Changes  |  Week of: August 23, 2026</t>
